--- a/AAII_Financials/Quarterly/FFMR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/FFMR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="92">
   <si>
     <t>FFMR</t>
   </si>
@@ -720,11 +720,11 @@
       <c r="E8" s="3">
         <v>17700</v>
       </c>
-      <c r="F8" s="3">
-        <v>17000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>17000</v>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H8" s="3">
         <v>16600</v>
@@ -732,8 +732,8 @@
       <c r="I8" s="3">
         <v>16600</v>
       </c>
-      <c r="J8" s="3">
-        <v>15600</v>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K8" s="3">
         <v>15600</v>
@@ -778,11 +778,11 @@
       <c r="E10" s="3">
         <v>17700</v>
       </c>
-      <c r="F10" s="3">
-        <v>17000</v>
-      </c>
-      <c r="G10" s="3">
-        <v>17000</v>
+      <c r="F10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H10" s="3">
         <v>16600</v>
@@ -790,8 +790,8 @@
       <c r="I10" s="3">
         <v>16600</v>
       </c>
-      <c r="J10" s="3">
-        <v>15600</v>
+      <c r="J10" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K10" s="3">
         <v>15600</v>
@@ -920,7 +920,7 @@
         <v>900</v>
       </c>
       <c r="J15" s="3">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3">
         <v>900</v>
@@ -946,11 +946,11 @@
       <c r="E17" s="3">
         <v>11200</v>
       </c>
-      <c r="F17" s="3">
-        <v>9500</v>
-      </c>
-      <c r="G17" s="3">
-        <v>9500</v>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H17" s="3">
         <v>9200</v>
@@ -958,8 +958,8 @@
       <c r="I17" s="3">
         <v>9200</v>
       </c>
-      <c r="J17" s="3">
-        <v>9900</v>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K17" s="3">
         <v>9900</v>
@@ -975,11 +975,11 @@
       <c r="E18" s="3">
         <v>6600</v>
       </c>
-      <c r="F18" s="3">
-        <v>7500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>7500</v>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H18" s="3">
         <v>7400</v>
@@ -987,8 +987,8 @@
       <c r="I18" s="3">
         <v>7400</v>
       </c>
-      <c r="J18" s="3">
-        <v>5700</v>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K18" s="3">
         <v>5700</v>
@@ -1017,11 +1017,11 @@
       <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
-        <v>400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>400</v>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H20" s="3">
         <v>400</v>
@@ -1029,8 +1029,8 @@
       <c r="I20" s="3">
         <v>400</v>
       </c>
-      <c r="J20" s="3">
-        <v>600</v>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K20" s="3">
         <v>600</v>
@@ -1047,10 +1047,10 @@
         <v>7100</v>
       </c>
       <c r="F21" s="3">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="G21" s="3">
-        <v>7200</v>
+        <v>0</v>
       </c>
       <c r="H21" s="3">
         <v>7900</v>
@@ -1059,7 +1059,7 @@
         <v>7900</v>
       </c>
       <c r="J21" s="3">
-        <v>6000</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3">
         <v>6000</v>
@@ -1104,11 +1104,11 @@
       <c r="E23" s="3">
         <v>6200</v>
       </c>
-      <c r="F23" s="3">
-        <v>7200</v>
-      </c>
-      <c r="G23" s="3">
-        <v>7200</v>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H23" s="3">
         <v>6100</v>
@@ -1116,8 +1116,8 @@
       <c r="I23" s="3">
         <v>6100</v>
       </c>
-      <c r="J23" s="3">
-        <v>5100</v>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K23" s="3">
         <v>5100</v>
@@ -1133,11 +1133,11 @@
       <c r="E24" s="3">
         <v>600</v>
       </c>
-      <c r="F24" s="3">
-        <v>1900</v>
-      </c>
-      <c r="G24" s="3">
-        <v>1900</v>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H24" s="3">
         <v>1500</v>
@@ -1145,8 +1145,8 @@
       <c r="I24" s="3">
         <v>1500</v>
       </c>
-      <c r="J24" s="3">
-        <v>1200</v>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K24" s="3">
         <v>1200</v>
@@ -1191,11 +1191,11 @@
       <c r="E26" s="3">
         <v>5600</v>
       </c>
-      <c r="F26" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>5300</v>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H26" s="3">
         <v>4600</v>
@@ -1203,8 +1203,8 @@
       <c r="I26" s="3">
         <v>4600</v>
       </c>
-      <c r="J26" s="3">
-        <v>3900</v>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K26" s="3">
         <v>3900</v>
@@ -1220,11 +1220,11 @@
       <c r="E27" s="3">
         <v>5600</v>
       </c>
-      <c r="F27" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G27" s="3">
-        <v>5300</v>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H27" s="3">
         <v>4600</v>
@@ -1232,8 +1232,8 @@
       <c r="I27" s="3">
         <v>4600</v>
       </c>
-      <c r="J27" s="3">
-        <v>3900</v>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K27" s="3">
         <v>3900</v>
@@ -1365,11 +1365,11 @@
       <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-400</v>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H32" s="3">
         <v>-400</v>
@@ -1377,8 +1377,8 @@
       <c r="I32" s="3">
         <v>-400</v>
       </c>
-      <c r="J32" s="3">
-        <v>-600</v>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K32" s="3">
         <v>-600</v>
@@ -1394,11 +1394,11 @@
       <c r="E33" s="3">
         <v>5600</v>
       </c>
-      <c r="F33" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G33" s="3">
-        <v>5300</v>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H33" s="3">
         <v>4600</v>
@@ -1406,8 +1406,8 @@
       <c r="I33" s="3">
         <v>4600</v>
       </c>
-      <c r="J33" s="3">
-        <v>3900</v>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K33" s="3">
         <v>3900</v>
@@ -1452,11 +1452,11 @@
       <c r="E35" s="3">
         <v>5600</v>
       </c>
-      <c r="F35" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G35" s="3">
-        <v>5300</v>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H35" s="3">
         <v>4600</v>
@@ -1464,8 +1464,8 @@
       <c r="I35" s="3">
         <v>4600</v>
       </c>
-      <c r="J35" s="3">
-        <v>3900</v>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K35" s="3">
         <v>3900</v>
@@ -1541,11 +1541,11 @@
       <c r="E41" s="3">
         <v>83600</v>
       </c>
-      <c r="F41" s="3">
-        <v>38800</v>
-      </c>
-      <c r="G41" s="3">
-        <v>38800</v>
+      <c r="F41" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H41" s="3">
         <v>107100</v>
@@ -1571,10 +1571,10 @@
         <v>4300</v>
       </c>
       <c r="F42" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>3100</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>3500</v>
@@ -1657,11 +1657,11 @@
       <c r="E45" s="3">
         <v>24000</v>
       </c>
-      <c r="F45" s="3">
-        <v>18900</v>
-      </c>
-      <c r="G45" s="3">
-        <v>18900</v>
+      <c r="F45" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H45" s="3">
         <v>20100</v>
@@ -1686,11 +1686,11 @@
       <c r="E46" s="3">
         <v>116300</v>
       </c>
-      <c r="F46" s="3">
-        <v>64200</v>
-      </c>
-      <c r="G46" s="3">
-        <v>64200</v>
+      <c r="F46" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H46" s="3">
         <v>138200</v>
@@ -1715,11 +1715,11 @@
       <c r="E47" s="3">
         <v>303000</v>
       </c>
-      <c r="F47" s="3">
-        <v>294700</v>
-      </c>
-      <c r="G47" s="3">
-        <v>294700</v>
+      <c r="F47" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H47" s="3">
         <v>287600</v>
@@ -1744,11 +1744,11 @@
       <c r="E48" s="3">
         <v>18000</v>
       </c>
-      <c r="F48" s="3">
-        <v>17800</v>
-      </c>
-      <c r="G48" s="3">
-        <v>17800</v>
+      <c r="F48" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H48" s="3">
         <v>18100</v>
@@ -1773,11 +1773,11 @@
       <c r="E49" s="3">
         <v>11100</v>
       </c>
-      <c r="F49" s="3">
-        <v>11600</v>
-      </c>
-      <c r="G49" s="3">
-        <v>11600</v>
+      <c r="F49" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H49" s="3">
         <v>12100</v>
@@ -1785,8 +1785,8 @@
       <c r="I49" s="3">
         <v>12100</v>
       </c>
-      <c r="J49" s="3">
-        <v>0</v>
+      <c r="J49" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K49" s="3">
         <v>0</v>
@@ -1860,11 +1860,11 @@
       <c r="E52" s="3">
         <v>13800</v>
       </c>
-      <c r="F52" s="3">
-        <v>13700</v>
-      </c>
-      <c r="G52" s="3">
-        <v>13700</v>
+      <c r="F52" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H52" s="3">
         <v>13000</v>
@@ -1918,11 +1918,11 @@
       <c r="E54" s="3">
         <v>1676700</v>
       </c>
-      <c r="F54" s="3">
-        <v>1600200</v>
-      </c>
-      <c r="G54" s="3">
-        <v>1600200</v>
+      <c r="F54" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H54" s="3">
         <v>1615600</v>
@@ -1973,11 +1973,11 @@
       <c r="E57" s="3">
         <v>1334700</v>
       </c>
-      <c r="F57" s="3">
-        <v>1266000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>1266000</v>
+      <c r="F57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H57" s="3">
         <v>1320700</v>
@@ -2002,11 +2002,11 @@
       <c r="E58" s="3">
         <v>0</v>
       </c>
-      <c r="F58" s="3">
-        <v>0</v>
-      </c>
-      <c r="G58" s="3">
-        <v>0</v>
+      <c r="F58" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H58" s="3">
         <v>0</v>
@@ -2014,8 +2014,8 @@
       <c r="I58" s="3">
         <v>0</v>
       </c>
-      <c r="J58" s="3">
-        <v>0</v>
+      <c r="J58" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2060,11 +2060,11 @@
       <c r="E60" s="3">
         <v>1349900</v>
       </c>
-      <c r="F60" s="3">
-        <v>1281600</v>
-      </c>
-      <c r="G60" s="3">
-        <v>1281600</v>
+      <c r="F60" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H60" s="3">
         <v>1339800</v>
@@ -2090,10 +2090,10 @@
         <v>173100</v>
       </c>
       <c r="F61" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="G61" s="3">
-        <v>172500</v>
+        <v>0</v>
       </c>
       <c r="H61" s="3">
         <v>140200</v>
@@ -2234,11 +2234,11 @@
       <c r="E66" s="3">
         <v>1522900</v>
       </c>
-      <c r="F66" s="3">
-        <v>1454000</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1454000</v>
+      <c r="F66" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G66" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H66" s="3">
         <v>1479900</v>
@@ -2392,11 +2392,11 @@
       <c r="E72" s="3">
         <v>146700</v>
       </c>
-      <c r="F72" s="3">
-        <v>138000</v>
-      </c>
-      <c r="G72" s="3">
-        <v>138000</v>
+      <c r="F72" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G72" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H72" s="3">
         <v>129800</v>
@@ -2508,11 +2508,11 @@
       <c r="E76" s="3">
         <v>153700</v>
       </c>
-      <c r="F76" s="3">
-        <v>146200</v>
-      </c>
-      <c r="G76" s="3">
-        <v>146200</v>
+      <c r="F76" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G76" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H76" s="3">
         <v>135600</v>
@@ -2600,11 +2600,11 @@
       <c r="E81" s="3">
         <v>5600</v>
       </c>
-      <c r="F81" s="3">
-        <v>5300</v>
-      </c>
-      <c r="G81" s="3">
-        <v>5300</v>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="H81" s="3">
         <v>4600</v>
@@ -2612,8 +2612,8 @@
       <c r="I81" s="3">
         <v>4600</v>
       </c>
-      <c r="J81" s="3">
-        <v>3900</v>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K81" s="3">
         <v>3900</v>
